--- a/Data/19_dataText/dataText.xlsx
+++ b/Data/19_dataText/dataText.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26130"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pjames2\OneDrive - Department for Education\Documents\RProjects\lsip_dashboard\Data\19_dataText\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D55532DF-1DCA-4BDC-93C2-A4B78AD0C889}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{991F491A-C201-44B2-BFC8-F2770D808600}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14660" xr2:uid="{E004AAF5-AC7D-409D-877C-9EBD23056743}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="177">
   <si>
     <t>empRate</t>
   </si>
@@ -54,9 +54,6 @@
   </si>
   <si>
     <t>vacancies</t>
-  </si>
-  <si>
-    <t>workingFutures</t>
   </si>
   <si>
     <t>enterpriseCount</t>
@@ -593,6 +590,33 @@
   </si>
   <si>
     <t>Dec 2020 - Dec 2021</t>
+  </si>
+  <si>
+    <t>wfEmployment</t>
+  </si>
+  <si>
+    <t>2035</t>
+  </si>
+  <si>
+    <t>To come</t>
+  </si>
+  <si>
+    <t>Forecasted employment</t>
+  </si>
+  <si>
+    <t>forecasted employment volumes</t>
+  </si>
+  <si>
+    <t>forecasted employment volume</t>
+  </si>
+  <si>
+    <t>Forecasted employment is</t>
+  </si>
+  <si>
+    <t>forecasted employment volume growth</t>
+  </si>
+  <si>
+    <t>Forecasted employment growth in</t>
   </si>
 </sst>
 </file>
@@ -1020,43 +1044,43 @@
   <sheetData>
     <row r="1" spans="1:13" ht="15" thickBot="1">
       <c r="A1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D1" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="C1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>20</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>21</v>
       </c>
-      <c r="F1" t="s">
-        <v>22</v>
-      </c>
       <c r="G1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H1" t="s">
+        <v>161</v>
+      </c>
+      <c r="I1" t="s">
         <v>162</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>163</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>164</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>165</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>166</v>
-      </c>
-      <c r="M1" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="73" thickBot="1">
@@ -1064,40 +1088,40 @@
         <v>0</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H2" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="I2" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="J2" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="J2" s="8" t="s">
+      <c r="K2" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="L2" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="K2" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="L2" s="8" t="s">
+      <c r="M2" s="8" t="s">
         <v>84</v>
-      </c>
-      <c r="M2" s="8" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="73" thickBot="1">
@@ -1105,40 +1129,40 @@
         <v>1</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H3" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="I3" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="J3" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="K3" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="M3" s="8" t="s">
         <v>88</v>
-      </c>
-      <c r="K3" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="L3" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="M3" s="8" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="73" thickBot="1">
@@ -1146,40 +1170,40 @@
         <v>2</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H4" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="J4" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="I4" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="J4" s="8" t="s">
+      <c r="K4" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="M4" s="8" t="s">
         <v>91</v>
-      </c>
-      <c r="K4" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="L4" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="M4" s="8" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="73" thickBot="1">
@@ -1187,40 +1211,40 @@
         <v>3</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H5" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="I5" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="I5" s="8" t="s">
+      <c r="J5" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="J5" s="8" t="s">
+      <c r="K5" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="M5" s="8" t="s">
         <v>95</v>
-      </c>
-      <c r="K5" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="L5" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="M5" s="8" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="174.5" thickBot="1">
@@ -1228,163 +1252,163 @@
         <v>4</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G6" s="8" t="s">
         <v>4</v>
       </c>
       <c r="H6" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="I6" s="8" t="s">
         <v>97</v>
-      </c>
-      <c r="I6" s="8" t="s">
-        <v>98</v>
       </c>
       <c r="J6" s="8" t="s">
         <v>4</v>
       </c>
       <c r="K6" s="8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L6" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="M6" s="8" t="s">
         <v>99</v>
-      </c>
-      <c r="M6" s="8" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="73" thickBot="1">
       <c r="A7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H7" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="I7" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="I7" s="8" t="s">
+      <c r="J7" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="L7" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="J7" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="K7" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="L7" s="8" t="s">
+      <c r="M7" s="8" t="s">
         <v>103</v>
-      </c>
-      <c r="M7" s="8" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="73" thickBot="1">
       <c r="A8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H8" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="I8" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="I8" s="8" t="s">
+      <c r="J8" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="K8" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="L8" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="J8" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="K8" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="L8" s="8" t="s">
+      <c r="M8" s="8" t="s">
         <v>107</v>
-      </c>
-      <c r="M8" s="8" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="73" thickBot="1">
       <c r="A9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H9" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="I9" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="I9" s="8" t="s">
+      <c r="J9" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="K9" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="L9" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="J9" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="K9" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="L9" s="8" t="s">
+      <c r="M9" s="8" t="s">
         <v>111</v>
-      </c>
-      <c r="M9" s="8" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="145.5" thickBot="1">
@@ -1392,503 +1416,532 @@
         <v>5</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H10" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="J10" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="I10" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="J10" s="8" t="s">
+      <c r="K10" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="L10" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="K10" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="L10" s="8" t="s">
+      <c r="M10" s="8" t="s">
         <v>115</v>
-      </c>
-      <c r="M10" s="8" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="87.5" thickBot="1">
       <c r="A11" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H11" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="I11" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="I11" s="8" t="s">
+      <c r="J11" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="J11" s="8" t="s">
+      <c r="K11" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="L11" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="K11" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="L11" s="8" t="s">
+      <c r="M11" s="8" t="s">
         <v>120</v>
-      </c>
-      <c r="M11" s="8" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="261.5" thickBot="1">
       <c r="A12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H12" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="I12" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="I12" s="8" t="s">
+      <c r="J12" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="J12" s="8" t="s">
+      <c r="K12" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="L12" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="K12" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="L12" s="8" t="s">
+      <c r="M12" s="8" t="s">
         <v>125</v>
-      </c>
-      <c r="M12" s="8" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="261.5" thickBot="1">
       <c r="A13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H13" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="I13" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="I13" s="8" t="s">
+      <c r="J13" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="J13" s="8" t="s">
+      <c r="K13" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="L13" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="K13" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="L13" s="8" t="s">
+      <c r="M13" s="8" t="s">
         <v>130</v>
-      </c>
-      <c r="M13" s="8" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="363" thickBot="1">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H14" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="I14" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="I14" s="8" t="s">
+      <c r="J14" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="J14" s="8" t="s">
+      <c r="K14" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="K14" s="8" t="s">
+      <c r="L14" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="L14" s="8" t="s">
+      <c r="M14" s="8" t="s">
         <v>136</v>
-      </c>
-      <c r="M14" s="8" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="363" thickBot="1">
       <c r="A15" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H15" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="I15" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="I15" s="8" t="s">
+      <c r="J15" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="K15" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="L15" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="J15" s="8" t="s">
-        <v>139</v>
-      </c>
-      <c r="K15" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="L15" s="8" t="s">
+      <c r="M15" s="8" t="s">
         <v>140</v>
-      </c>
-      <c r="M15" s="8" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="409.6" thickBot="1">
       <c r="A16" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H16" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="I16" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="J16" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="I16" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="J16" s="8" t="s">
+      <c r="K16" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="L16" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="M16" s="8" t="s">
         <v>143</v>
-      </c>
-      <c r="K16" s="8" t="s">
-        <v>142</v>
-      </c>
-      <c r="L16" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="M16" s="8" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="409.6" thickBot="1">
       <c r="A17" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H17" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="I17" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="J17" s="8" t="s">
         <v>145</v>
       </c>
-      <c r="I17" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="J17" s="8" t="s">
+      <c r="K17" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="L17" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="M17" s="8" t="s">
         <v>146</v>
-      </c>
-      <c r="K17" s="8" t="s">
-        <v>145</v>
-      </c>
-      <c r="L17" s="8" t="s">
-        <v>146</v>
-      </c>
-      <c r="M17" s="8" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="203.5" thickBot="1">
       <c r="A18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H18" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="I18" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="J18" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="I18" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="J18" s="8" t="s">
+      <c r="K18" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="L18" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="K18" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="L18" s="8" t="s">
+      <c r="M18" s="8" t="s">
         <v>150</v>
-      </c>
-      <c r="M18" s="8" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="263" thickBot="1">
       <c r="A19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E19" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="D19" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="F19" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H19" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="I19" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="J19" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="I19" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="J19" s="8" t="s">
+      <c r="K19" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="K19" s="8" t="s">
+      <c r="L19" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="L19" s="8" t="s">
+      <c r="M19" s="8" t="s">
         <v>155</v>
-      </c>
-      <c r="M19" s="8" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="254" thickBot="1">
       <c r="A20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C20" t="s">
+        <v>54</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E20" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D20" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>56</v>
-      </c>
       <c r="F20" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H20" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="I20" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="J20" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="I20" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="J20" s="8" t="s">
+      <c r="K20" s="8" t="s">
         <v>158</v>
       </c>
-      <c r="K20" s="8" t="s">
+      <c r="L20" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="L20" s="8" t="s">
+      <c r="M20" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="M20" s="8" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" ht="15" thickBot="1">
+    </row>
+    <row r="21" spans="1:13" ht="42.5" thickBot="1">
       <c r="A21" t="s">
-        <v>6</v>
+        <v>168</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>169</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>40</v>
+        <v>170</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>170</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="G21" s="8"/>
+        <v>170</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G21" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="H21" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="I21" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="J21" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="K21" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="L21" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="M21" s="8" t="s">
+        <v>174</v>
+      </c>
     </row>
     <row r="22" spans="1:13" ht="409.6" thickBot="1">
       <c r="A22" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D22" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G22" s="8"/>
     </row>
     <row r="23" spans="1:13" ht="363" thickBot="1">
       <c r="A23" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D23" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G23" s="8"/>
     </row>
